--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05 06:45:26 UTC</t>
+          <t>2026-09-06 06:55:20 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.40</t>
+          <t>20.31</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06 06:55:20 UTC</t>
+          <t>2026-09-07 07:05:12 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.22</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 07:05:12 UTC</t>
+          <t>2026-09-08 07:00:43 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>20.31</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 07:00:43 UTC</t>
+          <t>2026-09-09 07:09:23 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>20.45</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 07:09:23 UTC</t>
+          <t>2026-09-10 07:06:08 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.63</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 07:06:08 UTC</t>
+          <t>2026-09-11 07:05:25 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.49</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 07:05:25 UTC</t>
+          <t>2026-09-12 06:56:53 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>20.41</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 06:56:53 UTC</t>
+          <t>2026-09-13 07:14:47 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>20.29</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Reports/Summary_Report.xlsx
+++ b/reports/latest/Reports/Summary_Report.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 07:14:47 UTC</t>
+          <t>2026-09-14 07:38:34 UTC</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>20.32</t>
         </is>
       </c>
     </row>
